--- a/backend/data/financials_by_company/0KM.F.xlsx
+++ b/backend/data/financials_by_company/0KM.F.xlsx
@@ -682,622 +682,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-456237.726625</v>
+        <v>-25764</v>
       </c>
       <c r="C2" t="n">
-        <v>0.157432</v>
+        <v>0.228</v>
       </c>
       <c r="D2" t="n">
-        <v>47157000</v>
+        <v>61584000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2898000</v>
+        <v>-113000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2898000</v>
+        <v>-113000</v>
       </c>
       <c r="G2" t="n">
-        <v>17826000</v>
+        <v>26786000</v>
       </c>
       <c r="H2" t="n">
-        <v>14108000</v>
+        <v>17644000</v>
       </c>
       <c r="I2" t="n">
-        <v>225712000</v>
+        <v>237699000</v>
       </c>
       <c r="J2" t="n">
-        <v>44259000</v>
+        <v>61471000</v>
       </c>
       <c r="K2" t="n">
-        <v>30151000</v>
+        <v>43827000</v>
       </c>
       <c r="L2" t="n">
-        <v>-196000</v>
+        <v>-1139000</v>
       </c>
       <c r="M2" t="n">
-        <v>697000</v>
+        <v>1114000</v>
       </c>
       <c r="N2" t="n">
-        <v>540000</v>
+        <v>218000</v>
       </c>
       <c r="O2" t="n">
-        <v>20267762.273375</v>
+        <v>26873236</v>
       </c>
       <c r="P2" t="n">
-        <v>17826000</v>
+        <v>34404000</v>
       </c>
       <c r="Q2" t="n">
-        <v>282651000</v>
+        <v>289516000</v>
       </c>
       <c r="R2" t="n">
-        <v>27327000</v>
+        <v>45790000</v>
       </c>
       <c r="S2" t="n">
-        <v>35569072</v>
+        <v>43972523</v>
       </c>
       <c r="T2" t="n">
-        <v>35569072</v>
+        <v>43972523</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="W2" t="n">
-        <v>17826000</v>
+        <v>34404000</v>
       </c>
       <c r="X2" t="n">
-        <v>17826000</v>
+        <v>34404000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>17826000</v>
+        <v>34404000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6991000</v>
+        <v>-6122000</v>
       </c>
       <c r="AB2" t="n">
-        <v>24817000</v>
+        <v>40526000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7618000</v>
       </c>
       <c r="AD2" t="n">
-        <v>24817000</v>
+        <v>32908000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4637000</v>
+        <v>9805000</v>
       </c>
       <c r="AF2" t="n">
-        <v>29454000</v>
+        <v>42713000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3223000</v>
+        <v>832000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30000</v>
+        <v>-719000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-22000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3215000</v>
-      </c>
+        <v>-113000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-196000</v>
+        <v>-1139000</v>
       </c>
       <c r="AL2" t="n">
-        <v>39000</v>
+        <v>243000</v>
       </c>
       <c r="AM2" t="n">
-        <v>697000</v>
+        <v>1114000</v>
       </c>
       <c r="AN2" t="n">
-        <v>540000</v>
+        <v>218000</v>
       </c>
       <c r="AO2" t="n">
-        <v>30462000</v>
+        <v>44464000</v>
       </c>
       <c r="AP2" t="n">
-        <v>56939000</v>
+        <v>51817000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7416000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3646000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3646000</v>
-      </c>
+        <v>1638000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>30382000</v>
+        <v>51899000</v>
       </c>
       <c r="AU2" t="n">
-        <v>20134000</v>
+        <v>20523000</v>
       </c>
       <c r="AV2" t="n">
-        <v>10248000</v>
+        <v>31376000</v>
       </c>
       <c r="AW2" t="n">
-        <v>87401000</v>
+        <v>96281000</v>
       </c>
       <c r="AX2" t="n">
-        <v>225712000</v>
+        <v>237699000</v>
       </c>
       <c r="AY2" t="n">
-        <v>313113000</v>
+        <v>333980000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>313113000</v>
+        <v>333980000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-794227.708657</v>
+        <v>-151638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.177164</v>
+        <v>0.199</v>
       </c>
       <c r="D3" t="n">
-        <v>51824000</v>
+        <v>42260000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4483000</v>
+        <v>-762000</v>
       </c>
       <c r="F3" t="n">
-        <v>-4483000</v>
+        <v>-762000</v>
       </c>
       <c r="G3" t="n">
-        <v>22618000</v>
+        <v>11845000</v>
       </c>
       <c r="H3" t="n">
-        <v>14996000</v>
+        <v>17608000</v>
       </c>
       <c r="I3" t="n">
-        <v>252786000</v>
+        <v>321157000</v>
       </c>
       <c r="J3" t="n">
-        <v>47341000</v>
+        <v>41498000</v>
       </c>
       <c r="K3" t="n">
-        <v>32345000</v>
+        <v>23890000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1031000</v>
+        <v>-2849000</v>
       </c>
       <c r="M3" t="n">
-        <v>1481000</v>
+        <v>3001000</v>
       </c>
       <c r="N3" t="n">
-        <v>563000</v>
+        <v>302000</v>
       </c>
       <c r="O3" t="n">
-        <v>26306772.291343</v>
+        <v>12455362</v>
       </c>
       <c r="P3" t="n">
-        <v>22618000</v>
+        <v>35255000</v>
       </c>
       <c r="Q3" t="n">
-        <v>301784000</v>
+        <v>380487000</v>
       </c>
       <c r="R3" t="n">
-        <v>34454000</v>
+        <v>26318000</v>
       </c>
       <c r="S3" t="n">
-        <v>36867665</v>
+        <v>40801738</v>
       </c>
       <c r="T3" t="n">
-        <v>36867665</v>
+        <v>40801738</v>
       </c>
       <c r="U3" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="V3" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="W3" t="n">
-        <v>22618000</v>
+        <v>35255000</v>
       </c>
       <c r="X3" t="n">
-        <v>22618000</v>
+        <v>35255000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>22618000</v>
+        <v>35255000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2778000</v>
+        <v>-6332000</v>
       </c>
       <c r="AB3" t="n">
-        <v>25396000</v>
+        <v>41587000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>23410000</v>
       </c>
       <c r="AD3" t="n">
-        <v>25396000</v>
+        <v>18177000</v>
       </c>
       <c r="AE3" t="n">
-        <v>5468000</v>
+        <v>2712000</v>
       </c>
       <c r="AF3" t="n">
-        <v>30864000</v>
+        <v>20889000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4015000</v>
+        <v>145000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-101000</v>
+        <v>172000</v>
       </c>
       <c r="AI3" t="n">
-        <v>216000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3900000</v>
-      </c>
+        <v>-317000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-1031000</v>
+        <v>-2849000</v>
       </c>
       <c r="AL3" t="n">
-        <v>113000</v>
+        <v>150000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1481000</v>
+        <v>3001000</v>
       </c>
       <c r="AN3" t="n">
-        <v>563000</v>
+        <v>302000</v>
       </c>
       <c r="AO3" t="n">
-        <v>37866000</v>
+        <v>25435000</v>
       </c>
       <c r="AP3" t="n">
-        <v>48998000</v>
+        <v>59330000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8482000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3193000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3193000</v>
-      </c>
+        <v>2189000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>32972000</v>
+        <v>61334000</v>
       </c>
       <c r="AU3" t="n">
-        <v>23258000</v>
+        <v>27418000</v>
       </c>
       <c r="AV3" t="n">
-        <v>9714000</v>
+        <v>33916000</v>
       </c>
       <c r="AW3" t="n">
-        <v>86864000</v>
+        <v>84765000</v>
       </c>
       <c r="AX3" t="n">
-        <v>252786000</v>
+        <v>321157000</v>
       </c>
       <c r="AY3" t="n">
-        <v>339650000</v>
+        <v>405922000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>339650000</v>
+        <v>405922000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-151638</v>
+        <v>-794227.708657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.199</v>
+        <v>0.177164</v>
       </c>
       <c r="D4" t="n">
-        <v>42260000</v>
+        <v>51824000</v>
       </c>
       <c r="E4" t="n">
-        <v>-762000</v>
+        <v>-4483000</v>
       </c>
       <c r="F4" t="n">
-        <v>-762000</v>
+        <v>-4483000</v>
       </c>
       <c r="G4" t="n">
-        <v>11845000</v>
+        <v>22618000</v>
       </c>
       <c r="H4" t="n">
-        <v>17608000</v>
+        <v>14996000</v>
       </c>
       <c r="I4" t="n">
-        <v>321157000</v>
+        <v>252786000</v>
       </c>
       <c r="J4" t="n">
-        <v>41498000</v>
+        <v>47341000</v>
       </c>
       <c r="K4" t="n">
-        <v>23890000</v>
+        <v>32345000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2849000</v>
+        <v>-1031000</v>
       </c>
       <c r="M4" t="n">
-        <v>3001000</v>
+        <v>1481000</v>
       </c>
       <c r="N4" t="n">
-        <v>302000</v>
+        <v>563000</v>
       </c>
       <c r="O4" t="n">
-        <v>12455362</v>
+        <v>26306772.291343</v>
       </c>
       <c r="P4" t="n">
-        <v>35255000</v>
+        <v>22618000</v>
       </c>
       <c r="Q4" t="n">
-        <v>380487000</v>
+        <v>301784000</v>
       </c>
       <c r="R4" t="n">
-        <v>26318000</v>
+        <v>34454000</v>
       </c>
       <c r="S4" t="n">
-        <v>40801738</v>
+        <v>36867665</v>
       </c>
       <c r="T4" t="n">
-        <v>40801738</v>
+        <v>36867665</v>
       </c>
       <c r="U4" t="n">
-        <v>0.86</v>
+        <v>0.61</v>
       </c>
       <c r="V4" t="n">
-        <v>0.86</v>
+        <v>0.61</v>
       </c>
       <c r="W4" t="n">
-        <v>35255000</v>
+        <v>22618000</v>
       </c>
       <c r="X4" t="n">
-        <v>35255000</v>
+        <v>22618000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>35255000</v>
+        <v>22618000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6332000</v>
+        <v>-2778000</v>
       </c>
       <c r="AB4" t="n">
-        <v>41587000</v>
+        <v>25396000</v>
       </c>
       <c r="AC4" t="n">
-        <v>23410000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>18177000</v>
+        <v>25396000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2712000</v>
+        <v>5468000</v>
       </c>
       <c r="AF4" t="n">
-        <v>20889000</v>
+        <v>30864000</v>
       </c>
       <c r="AG4" t="n">
-        <v>145000</v>
+        <v>-4015000</v>
       </c>
       <c r="AH4" t="n">
-        <v>172000</v>
+        <v>-101000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-317000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>216000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3900000</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-2849000</v>
+        <v>-1031000</v>
       </c>
       <c r="AL4" t="n">
-        <v>150000</v>
+        <v>113000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3001000</v>
+        <v>1481000</v>
       </c>
       <c r="AN4" t="n">
-        <v>302000</v>
+        <v>563000</v>
       </c>
       <c r="AO4" t="n">
-        <v>25435000</v>
+        <v>37866000</v>
       </c>
       <c r="AP4" t="n">
-        <v>59330000</v>
+        <v>48998000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2189000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+        <v>8482000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3193000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3193000</v>
+      </c>
       <c r="AT4" t="n">
-        <v>61334000</v>
+        <v>32972000</v>
       </c>
       <c r="AU4" t="n">
-        <v>27418000</v>
+        <v>23258000</v>
       </c>
       <c r="AV4" t="n">
-        <v>33916000</v>
+        <v>9714000</v>
       </c>
       <c r="AW4" t="n">
-        <v>84765000</v>
+        <v>86864000</v>
       </c>
       <c r="AX4" t="n">
-        <v>321157000</v>
+        <v>252786000</v>
       </c>
       <c r="AY4" t="n">
-        <v>405922000</v>
+        <v>339650000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>405922000</v>
+        <v>339650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-25764</v>
+        <v>-456237.726625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.228</v>
+        <v>0.157432</v>
       </c>
       <c r="D5" t="n">
-        <v>61584000</v>
+        <v>47157000</v>
       </c>
       <c r="E5" t="n">
-        <v>-113000</v>
+        <v>-2898000</v>
       </c>
       <c r="F5" t="n">
-        <v>-113000</v>
+        <v>-2898000</v>
       </c>
       <c r="G5" t="n">
-        <v>26786000</v>
+        <v>17826000</v>
       </c>
       <c r="H5" t="n">
-        <v>17644000</v>
+        <v>14108000</v>
       </c>
       <c r="I5" t="n">
-        <v>237699000</v>
+        <v>225712000</v>
       </c>
       <c r="J5" t="n">
-        <v>61471000</v>
+        <v>44259000</v>
       </c>
       <c r="K5" t="n">
-        <v>43827000</v>
+        <v>30151000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1139000</v>
+        <v>-196000</v>
       </c>
       <c r="M5" t="n">
-        <v>1114000</v>
+        <v>697000</v>
       </c>
       <c r="N5" t="n">
-        <v>218000</v>
+        <v>540000</v>
       </c>
       <c r="O5" t="n">
-        <v>26873236</v>
+        <v>20267762.273375</v>
       </c>
       <c r="P5" t="n">
-        <v>34404000</v>
+        <v>17826000</v>
       </c>
       <c r="Q5" t="n">
-        <v>289516000</v>
+        <v>282651000</v>
       </c>
       <c r="R5" t="n">
-        <v>45790000</v>
+        <v>27327000</v>
       </c>
       <c r="S5" t="n">
-        <v>43972523</v>
+        <v>35569072</v>
       </c>
       <c r="T5" t="n">
-        <v>43972523</v>
+        <v>35569072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>34404000</v>
+        <v>17826000</v>
       </c>
       <c r="X5" t="n">
-        <v>34404000</v>
+        <v>17826000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>34404000</v>
+        <v>17826000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6122000</v>
+        <v>-6991000</v>
       </c>
       <c r="AB5" t="n">
-        <v>40526000</v>
+        <v>24817000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7618000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>32908000</v>
+        <v>24817000</v>
       </c>
       <c r="AE5" t="n">
-        <v>9805000</v>
+        <v>4637000</v>
       </c>
       <c r="AF5" t="n">
-        <v>42713000</v>
+        <v>29454000</v>
       </c>
       <c r="AG5" t="n">
-        <v>832000</v>
+        <v>-3223000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-719000</v>
+        <v>30000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-113000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-22000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3215000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-1139000</v>
+        <v>-196000</v>
       </c>
       <c r="AL5" t="n">
-        <v>243000</v>
+        <v>39000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1114000</v>
+        <v>697000</v>
       </c>
       <c r="AN5" t="n">
-        <v>218000</v>
+        <v>540000</v>
       </c>
       <c r="AO5" t="n">
-        <v>44464000</v>
+        <v>30462000</v>
       </c>
       <c r="AP5" t="n">
-        <v>51817000</v>
+        <v>56939000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1638000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+        <v>7416000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3646000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3646000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>51899000</v>
+        <v>30382000</v>
       </c>
       <c r="AU5" t="n">
-        <v>20523000</v>
+        <v>20134000</v>
       </c>
       <c r="AV5" t="n">
-        <v>31376000</v>
+        <v>10248000</v>
       </c>
       <c r="AW5" t="n">
-        <v>96281000</v>
+        <v>87401000</v>
       </c>
       <c r="AX5" t="n">
-        <v>237699000</v>
+        <v>225712000</v>
       </c>
       <c r="AY5" t="n">
-        <v>333980000</v>
+        <v>313113000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>333980000</v>
+        <v>313113000</v>
       </c>
     </row>
   </sheetData>
@@ -1693,277 +1693,277 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>4817267</v>
+        <v>2442917</v>
       </c>
       <c r="C2" t="n">
-        <v>35182733</v>
+        <v>43972523</v>
       </c>
       <c r="D2" t="n">
-        <v>40000000</v>
+        <v>46415440</v>
       </c>
       <c r="E2" t="n">
-        <v>19594000</v>
+        <v>69603000</v>
       </c>
       <c r="F2" t="n">
-        <v>214129000</v>
+        <v>240131000</v>
       </c>
       <c r="G2" t="n">
-        <v>253435000</v>
+        <v>333026000</v>
       </c>
       <c r="H2" t="n">
-        <v>131207000</v>
+        <v>124548000</v>
       </c>
       <c r="I2" t="n">
-        <v>214129000</v>
+        <v>240131000</v>
       </c>
       <c r="J2" t="n">
-        <v>19594000</v>
+        <v>23138000</v>
       </c>
       <c r="K2" t="n">
-        <v>253435000</v>
+        <v>286561000</v>
       </c>
       <c r="L2" t="n">
-        <v>253435000</v>
+        <v>286561000</v>
       </c>
       <c r="M2" t="n">
-        <v>377661000</v>
+        <v>407762000</v>
       </c>
       <c r="N2" t="n">
-        <v>124226000</v>
+        <v>121201000</v>
       </c>
       <c r="O2" t="n">
-        <v>253435000</v>
+        <v>286561000</v>
       </c>
       <c r="P2" t="n">
-        <v>60293000</v>
+        <v>25713000</v>
       </c>
       <c r="Q2" t="n">
-        <v>217729000</v>
+        <v>211746000</v>
       </c>
       <c r="R2" t="n">
         <v>79525000</v>
       </c>
       <c r="S2" t="n">
-        <v>16400000</v>
+        <v>19030000</v>
       </c>
       <c r="T2" t="n">
-        <v>16400000</v>
+        <v>19030000</v>
       </c>
       <c r="U2" t="n">
-        <v>84775000</v>
+        <v>147850000</v>
       </c>
       <c r="V2" t="n">
-        <v>41915000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>27000</v>
-      </c>
+        <v>43753000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>22720000</v>
+        <v>21419000</v>
       </c>
       <c r="Y2" t="n">
-        <v>18054000</v>
+        <v>20385000</v>
       </c>
       <c r="Z2" t="n">
-        <v>18054000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>20385000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>1114000</v>
+        <v>1949000</v>
       </c>
       <c r="AC2" t="n">
-        <v>42860000</v>
+        <v>104097000</v>
       </c>
       <c r="AD2" t="n">
-        <v>10752000</v>
+        <v>3420000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1540000</v>
+        <v>49218000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1540000</v>
+        <v>2753000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>46465000</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>4325000</v>
+        <v>3261000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25985000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>38662000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>531000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5411000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>25985000</v>
+        <v>32720000</v>
       </c>
       <c r="AN2" t="n">
-        <v>462436000</v>
+        <v>555612000</v>
       </c>
       <c r="AO2" t="n">
-        <v>288369000</v>
+        <v>326967000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1552000</v>
+        <v>1261000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10000</v>
+        <v>18015000</v>
       </c>
       <c r="AR2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>30244000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>30244000</v>
-      </c>
+        <v>18015000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>27333000</v>
+        <v>26434000</v>
       </c>
       <c r="AV2" t="n">
-        <v>39306000</v>
+        <v>46430000</v>
       </c>
       <c r="AW2" t="n">
-        <v>27841000</v>
+        <v>34089000</v>
       </c>
       <c r="AX2" t="n">
-        <v>11465000</v>
+        <v>12341000</v>
       </c>
       <c r="AY2" t="n">
-        <v>189924000</v>
+        <v>234827000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-174960000</v>
+        <v>-212906000</v>
       </c>
       <c r="BA2" t="n">
-        <v>364884000</v>
+        <v>447733000</v>
       </c>
       <c r="BB2" t="n">
-        <v>1744000</v>
+        <v>21412000</v>
       </c>
       <c r="BC2" t="n">
-        <v>5124000</v>
+        <v>8818000</v>
       </c>
       <c r="BD2" t="n">
-        <v>250922000</v>
+        <v>292606000</v>
       </c>
       <c r="BE2" t="n">
-        <v>93149000</v>
+        <v>110536000</v>
       </c>
       <c r="BF2" t="n">
-        <v>13945000</v>
+        <v>14361000</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>174067000</v>
+        <v>228645000</v>
       </c>
       <c r="BI2" t="n">
-        <v>103000</v>
+        <v>111000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>536000</v>
+        <v>1226000</v>
       </c>
       <c r="BK2" t="n">
-        <v>86327000</v>
+        <v>98419000</v>
       </c>
       <c r="BL2" t="n">
-        <v>34998000</v>
+        <v>39627000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9319000</v>
+        <v>7510000</v>
       </c>
       <c r="BN2" t="n">
-        <v>42010000</v>
+        <v>51282000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3487000</v>
+        <v>3036000</v>
       </c>
       <c r="BP2" t="n">
-        <v>727000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>49081000</v>
+        <v>64414000</v>
       </c>
       <c r="BR2" t="n">
-        <v>-3481000</v>
+        <v>-3894000</v>
       </c>
       <c r="BS2" t="n">
-        <v>52562000</v>
+        <v>68308000</v>
       </c>
       <c r="BT2" t="n">
-        <v>33806000</v>
+        <v>61439000</v>
       </c>
       <c r="BU2" t="n">
-        <v>808000</v>
+        <v>3381000</v>
       </c>
       <c r="BV2" t="n">
-        <v>32998000</v>
+        <v>58058000</v>
       </c>
       <c r="BW2" t="n">
-        <v>15888000</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>17110000</v>
+        <v>58058000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3417267</v>
+        <v>817267</v>
       </c>
       <c r="C3" t="n">
-        <v>36582733</v>
+        <v>39182733</v>
       </c>
       <c r="D3" t="n">
         <v>40000000</v>
       </c>
       <c r="E3" t="n">
-        <v>20089000</v>
+        <v>21636000</v>
       </c>
       <c r="F3" t="n">
-        <v>209305000</v>
+        <v>216302000</v>
       </c>
       <c r="G3" t="n">
-        <v>251669000</v>
+        <v>263497000</v>
       </c>
       <c r="H3" t="n">
-        <v>132633000</v>
+        <v>135544000</v>
       </c>
       <c r="I3" t="n">
-        <v>209305000</v>
+        <v>216302000</v>
       </c>
       <c r="J3" t="n">
-        <v>20084000</v>
+        <v>21628000</v>
       </c>
       <c r="K3" t="n">
-        <v>251664000</v>
+        <v>263489000</v>
       </c>
       <c r="L3" t="n">
-        <v>251664000</v>
+        <v>263489000</v>
       </c>
       <c r="M3" t="n">
-        <v>366550000</v>
+        <v>384130000</v>
       </c>
       <c r="N3" t="n">
-        <v>114886000</v>
+        <v>120641000</v>
       </c>
       <c r="O3" t="n">
-        <v>251664000</v>
+        <v>263489000</v>
       </c>
       <c r="P3" t="n">
-        <v>42769000</v>
+        <v>10237000</v>
       </c>
       <c r="Q3" t="n">
-        <v>197287000</v>
+        <v>175586000</v>
       </c>
       <c r="R3" t="n">
         <v>79525000</v>
@@ -1975,111 +1975,107 @@
         <v>16400000</v>
       </c>
       <c r="U3" t="n">
-        <v>78229000</v>
+        <v>88445000</v>
       </c>
       <c r="V3" t="n">
-        <v>39883000</v>
+        <v>39193000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>20060000</v>
+        <v>19381000</v>
       </c>
       <c r="Y3" t="n">
-        <v>18670000</v>
+        <v>18769000</v>
       </c>
       <c r="Z3" t="n">
-        <v>18670000</v>
+        <v>18769000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1153000</v>
+        <v>1043000</v>
       </c>
       <c r="AC3" t="n">
-        <v>38346000</v>
+        <v>49252000</v>
       </c>
       <c r="AD3" t="n">
-        <v>724000</v>
+        <v>1308000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1419000</v>
+        <v>2867000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1414000</v>
+        <v>2859000</v>
       </c>
       <c r="AG3" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2669000</v>
+        <v>2334000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3581000</v>
+        <v>4245000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25081000</v>
+        <v>34817000</v>
       </c>
       <c r="AK3" t="n">
-        <v>567000</v>
+        <v>550000</v>
       </c>
       <c r="AL3" t="n">
-        <v>748000</v>
+        <v>2349000</v>
       </c>
       <c r="AM3" t="n">
-        <v>23766000</v>
+        <v>31918000</v>
       </c>
       <c r="AN3" t="n">
-        <v>444779000</v>
+        <v>472575000</v>
       </c>
       <c r="AO3" t="n">
-        <v>273800000</v>
+        <v>287779000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1624000</v>
+        <v>1734000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13261000</v>
+        <v>15982000</v>
       </c>
       <c r="AR3" t="n">
-        <v>13261000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
+        <v>15982000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>27261000</v>
+        <v>27077000</v>
       </c>
       <c r="AV3" t="n">
-        <v>42359000</v>
+        <v>47187000</v>
       </c>
       <c r="AW3" t="n">
-        <v>30692000</v>
+        <v>34603000</v>
       </c>
       <c r="AX3" t="n">
-        <v>11667000</v>
+        <v>12584000</v>
       </c>
       <c r="AY3" t="n">
-        <v>189295000</v>
+        <v>195799000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-164097000</v>
+        <v>-151265000</v>
       </c>
       <c r="BA3" t="n">
-        <v>353392000</v>
+        <v>347064000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1595000</v>
+        <v>1798000</v>
       </c>
       <c r="BC3" t="n">
-        <v>5747000</v>
+        <v>6593000</v>
       </c>
       <c r="BD3" t="n">
-        <v>242472000</v>
+        <v>236584000</v>
       </c>
       <c r="BE3" t="n">
-        <v>89582000</v>
+        <v>88093000</v>
       </c>
       <c r="BF3" t="n">
         <v>13996000</v>
@@ -2088,108 +2084,108 @@
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>170979000</v>
+        <v>184796000</v>
       </c>
       <c r="BI3" t="n">
-        <v>102000</v>
+        <v>285000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2325000</v>
+        <v>331000</v>
       </c>
       <c r="BK3" t="n">
-        <v>79329000</v>
+        <v>87925000</v>
       </c>
       <c r="BL3" t="n">
-        <v>32219000</v>
+        <v>33354000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8439000</v>
+        <v>8508000</v>
       </c>
       <c r="BN3" t="n">
-        <v>38671000</v>
+        <v>46063000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3445000</v>
+        <v>3357000</v>
       </c>
       <c r="BP3" t="n">
-        <v>1008000</v>
+        <v>4202000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>46765000</v>
+        <v>65523000</v>
       </c>
       <c r="BR3" t="n">
-        <v>-3826000</v>
+        <v>-4042000</v>
       </c>
       <c r="BS3" t="n">
-        <v>50590000</v>
+        <v>69565000</v>
       </c>
       <c r="BT3" t="n">
-        <v>38005000</v>
+        <v>23173000</v>
       </c>
       <c r="BU3" t="n">
-        <v>485000</v>
+        <v>1287000</v>
       </c>
       <c r="BV3" t="n">
-        <v>37520000</v>
+        <v>21886000</v>
       </c>
       <c r="BW3" t="n">
-        <v>24438000</v>
+        <v>3550000</v>
       </c>
       <c r="BX3" t="n">
-        <v>13082000</v>
+        <v>18336000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>817267</v>
+        <v>3417267</v>
       </c>
       <c r="C4" t="n">
-        <v>39182733</v>
+        <v>36582733</v>
       </c>
       <c r="D4" t="n">
         <v>40000000</v>
       </c>
       <c r="E4" t="n">
-        <v>21636000</v>
+        <v>20089000</v>
       </c>
       <c r="F4" t="n">
-        <v>216302000</v>
+        <v>209305000</v>
       </c>
       <c r="G4" t="n">
-        <v>263497000</v>
+        <v>251669000</v>
       </c>
       <c r="H4" t="n">
-        <v>135544000</v>
+        <v>132633000</v>
       </c>
       <c r="I4" t="n">
-        <v>216302000</v>
+        <v>209305000</v>
       </c>
       <c r="J4" t="n">
-        <v>21628000</v>
+        <v>20084000</v>
       </c>
       <c r="K4" t="n">
-        <v>263489000</v>
+        <v>251664000</v>
       </c>
       <c r="L4" t="n">
-        <v>263489000</v>
+        <v>251664000</v>
       </c>
       <c r="M4" t="n">
-        <v>384130000</v>
+        <v>366550000</v>
       </c>
       <c r="N4" t="n">
-        <v>120641000</v>
+        <v>114886000</v>
       </c>
       <c r="O4" t="n">
-        <v>263489000</v>
+        <v>251664000</v>
       </c>
       <c r="P4" t="n">
-        <v>10237000</v>
+        <v>42769000</v>
       </c>
       <c r="Q4" t="n">
-        <v>175586000</v>
+        <v>197287000</v>
       </c>
       <c r="R4" t="n">
         <v>79525000</v>
@@ -2201,107 +2197,111 @@
         <v>16400000</v>
       </c>
       <c r="U4" t="n">
-        <v>88445000</v>
+        <v>78229000</v>
       </c>
       <c r="V4" t="n">
-        <v>39193000</v>
+        <v>39883000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>19381000</v>
+        <v>20060000</v>
       </c>
       <c r="Y4" t="n">
-        <v>18769000</v>
+        <v>18670000</v>
       </c>
       <c r="Z4" t="n">
-        <v>18769000</v>
+        <v>18670000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>1043000</v>
+        <v>1153000</v>
       </c>
       <c r="AC4" t="n">
-        <v>49252000</v>
+        <v>38346000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1308000</v>
+        <v>724000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2867000</v>
+        <v>1419000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2859000</v>
+        <v>1414000</v>
       </c>
       <c r="AG4" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2334000</v>
+        <v>2669000</v>
       </c>
       <c r="AI4" t="n">
-        <v>4245000</v>
+        <v>3581000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34817000</v>
+        <v>25081000</v>
       </c>
       <c r="AK4" t="n">
-        <v>550000</v>
+        <v>567000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2349000</v>
+        <v>748000</v>
       </c>
       <c r="AM4" t="n">
-        <v>31918000</v>
+        <v>23766000</v>
       </c>
       <c r="AN4" t="n">
-        <v>472575000</v>
+        <v>444779000</v>
       </c>
       <c r="AO4" t="n">
-        <v>287779000</v>
+        <v>273800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1734000</v>
+        <v>1624000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15982000</v>
+        <v>13261000</v>
       </c>
       <c r="AR4" t="n">
-        <v>15982000</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>13261000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
       <c r="AU4" t="n">
-        <v>27077000</v>
+        <v>27261000</v>
       </c>
       <c r="AV4" t="n">
-        <v>47187000</v>
+        <v>42359000</v>
       </c>
       <c r="AW4" t="n">
-        <v>34603000</v>
+        <v>30692000</v>
       </c>
       <c r="AX4" t="n">
-        <v>12584000</v>
+        <v>11667000</v>
       </c>
       <c r="AY4" t="n">
-        <v>195799000</v>
+        <v>189295000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-151265000</v>
+        <v>-164097000</v>
       </c>
       <c r="BA4" t="n">
-        <v>347064000</v>
+        <v>353392000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1798000</v>
+        <v>1595000</v>
       </c>
       <c r="BC4" t="n">
-        <v>6593000</v>
+        <v>5747000</v>
       </c>
       <c r="BD4" t="n">
-        <v>236584000</v>
+        <v>242472000</v>
       </c>
       <c r="BE4" t="n">
-        <v>88093000</v>
+        <v>89582000</v>
       </c>
       <c r="BF4" t="n">
         <v>13996000</v>
@@ -2310,277 +2310,277 @@
         <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>184796000</v>
+        <v>170979000</v>
       </c>
       <c r="BI4" t="n">
-        <v>285000</v>
+        <v>102000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>331000</v>
+        <v>2325000</v>
       </c>
       <c r="BK4" t="n">
-        <v>87925000</v>
+        <v>79329000</v>
       </c>
       <c r="BL4" t="n">
-        <v>33354000</v>
+        <v>32219000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8508000</v>
+        <v>8439000</v>
       </c>
       <c r="BN4" t="n">
-        <v>46063000</v>
+        <v>38671000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3357000</v>
+        <v>3445000</v>
       </c>
       <c r="BP4" t="n">
-        <v>4202000</v>
+        <v>1008000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>65523000</v>
+        <v>46765000</v>
       </c>
       <c r="BR4" t="n">
-        <v>-4042000</v>
+        <v>-3826000</v>
       </c>
       <c r="BS4" t="n">
-        <v>69565000</v>
+        <v>50590000</v>
       </c>
       <c r="BT4" t="n">
-        <v>23173000</v>
+        <v>38005000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1287000</v>
+        <v>485000</v>
       </c>
       <c r="BV4" t="n">
-        <v>21886000</v>
+        <v>37520000</v>
       </c>
       <c r="BW4" t="n">
-        <v>3550000</v>
+        <v>24438000</v>
       </c>
       <c r="BX4" t="n">
-        <v>18336000</v>
+        <v>13082000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2442917</v>
+        <v>4817267</v>
       </c>
       <c r="C5" t="n">
-        <v>43972523</v>
+        <v>35182733</v>
       </c>
       <c r="D5" t="n">
-        <v>46415440</v>
+        <v>40000000</v>
       </c>
       <c r="E5" t="n">
-        <v>69603000</v>
+        <v>19594000</v>
       </c>
       <c r="F5" t="n">
-        <v>240131000</v>
+        <v>214129000</v>
       </c>
       <c r="G5" t="n">
-        <v>333026000</v>
+        <v>253435000</v>
       </c>
       <c r="H5" t="n">
-        <v>124548000</v>
+        <v>131207000</v>
       </c>
       <c r="I5" t="n">
-        <v>240131000</v>
+        <v>214129000</v>
       </c>
       <c r="J5" t="n">
-        <v>23138000</v>
+        <v>19594000</v>
       </c>
       <c r="K5" t="n">
-        <v>286561000</v>
+        <v>253435000</v>
       </c>
       <c r="L5" t="n">
-        <v>286561000</v>
+        <v>253435000</v>
       </c>
       <c r="M5" t="n">
-        <v>407762000</v>
+        <v>377661000</v>
       </c>
       <c r="N5" t="n">
-        <v>121201000</v>
+        <v>124226000</v>
       </c>
       <c r="O5" t="n">
-        <v>286561000</v>
+        <v>253435000</v>
       </c>
       <c r="P5" t="n">
-        <v>25713000</v>
+        <v>60293000</v>
       </c>
       <c r="Q5" t="n">
-        <v>211746000</v>
+        <v>217729000</v>
       </c>
       <c r="R5" t="n">
         <v>79525000</v>
       </c>
       <c r="S5" t="n">
-        <v>19030000</v>
+        <v>16400000</v>
       </c>
       <c r="T5" t="n">
-        <v>19030000</v>
+        <v>16400000</v>
       </c>
       <c r="U5" t="n">
-        <v>147850000</v>
+        <v>84775000</v>
       </c>
       <c r="V5" t="n">
-        <v>43753000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>41915000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>27000</v>
+      </c>
       <c r="X5" t="n">
-        <v>21419000</v>
+        <v>22720000</v>
       </c>
       <c r="Y5" t="n">
-        <v>20385000</v>
+        <v>18054000</v>
       </c>
       <c r="Z5" t="n">
-        <v>20385000</v>
-      </c>
-      <c r="AA5" t="n">
+        <v>18054000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>1114000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>42860000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10752000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1949000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>104097000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3420000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>49218000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2753000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>46465000</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>3261000</v>
+        <v>4325000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38662000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>531000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5411000</v>
-      </c>
+        <v>25985000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>32720000</v>
+        <v>25985000</v>
       </c>
       <c r="AN5" t="n">
-        <v>555612000</v>
+        <v>462436000</v>
       </c>
       <c r="AO5" t="n">
-        <v>326967000</v>
+        <v>288369000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1261000</v>
+        <v>1552000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18015000</v>
+        <v>10000</v>
       </c>
       <c r="AR5" t="n">
-        <v>18015000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>30244000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>30244000</v>
+      </c>
       <c r="AU5" t="n">
-        <v>26434000</v>
+        <v>27333000</v>
       </c>
       <c r="AV5" t="n">
-        <v>46430000</v>
+        <v>39306000</v>
       </c>
       <c r="AW5" t="n">
-        <v>34089000</v>
+        <v>27841000</v>
       </c>
       <c r="AX5" t="n">
-        <v>12341000</v>
+        <v>11465000</v>
       </c>
       <c r="AY5" t="n">
-        <v>234827000</v>
+        <v>189924000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-212906000</v>
+        <v>-174960000</v>
       </c>
       <c r="BA5" t="n">
-        <v>447733000</v>
+        <v>364884000</v>
       </c>
       <c r="BB5" t="n">
-        <v>21412000</v>
+        <v>1744000</v>
       </c>
       <c r="BC5" t="n">
-        <v>8818000</v>
+        <v>5124000</v>
       </c>
       <c r="BD5" t="n">
-        <v>292606000</v>
+        <v>250922000</v>
       </c>
       <c r="BE5" t="n">
-        <v>110536000</v>
+        <v>93149000</v>
       </c>
       <c r="BF5" t="n">
-        <v>14361000</v>
+        <v>13945000</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>228645000</v>
+        <v>174067000</v>
       </c>
       <c r="BI5" t="n">
-        <v>111000</v>
+        <v>103000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1226000</v>
+        <v>536000</v>
       </c>
       <c r="BK5" t="n">
-        <v>98419000</v>
+        <v>86327000</v>
       </c>
       <c r="BL5" t="n">
-        <v>39627000</v>
+        <v>34998000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7510000</v>
+        <v>9319000</v>
       </c>
       <c r="BN5" t="n">
-        <v>51282000</v>
+        <v>42010000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3036000</v>
+        <v>3487000</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>727000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>64414000</v>
+        <v>49081000</v>
       </c>
       <c r="BR5" t="n">
-        <v>-3894000</v>
+        <v>-3481000</v>
       </c>
       <c r="BS5" t="n">
-        <v>68308000</v>
+        <v>52562000</v>
       </c>
       <c r="BT5" t="n">
-        <v>61439000</v>
+        <v>33806000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3381000</v>
+        <v>808000</v>
       </c>
       <c r="BV5" t="n">
-        <v>58058000</v>
+        <v>32998000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>15888000</v>
       </c>
       <c r="BX5" t="n">
-        <v>58058000</v>
+        <v>17110000</v>
       </c>
     </row>
   </sheetData>
@@ -2826,528 +2826,528 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>18101000</v>
+        <v>12349000</v>
       </c>
       <c r="C2" t="n">
-        <v>-17524000</v>
+        <v>-14000</v>
       </c>
       <c r="D2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>-30039000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43017000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-13755000</v>
+        <v>-24113000</v>
       </c>
       <c r="G2" t="n">
-        <v>32998000</v>
+        <v>58058000</v>
       </c>
       <c r="H2" t="n">
-        <v>37520000</v>
+        <v>21630000</v>
       </c>
       <c r="I2" t="n">
-        <v>270000</v>
+        <v>40000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4792000</v>
+        <v>36388000</v>
       </c>
       <c r="K2" t="n">
-        <v>-16865000</v>
+        <v>-3217000</v>
       </c>
       <c r="L2" t="n">
-        <v>4408000</v>
+        <v>1826000</v>
       </c>
       <c r="M2" t="n">
-        <v>-684000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-908000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-13192000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-17524000</v>
+        <v>-14000</v>
       </c>
       <c r="P2" t="n">
-        <v>-17524000</v>
+        <v>-14000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5000</v>
+        <v>12978000</v>
       </c>
       <c r="R2" t="n">
-        <v>-5000</v>
+        <v>12978000</v>
       </c>
       <c r="S2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>-30039000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>43017000</v>
+      </c>
       <c r="U2" t="n">
-        <v>-19783000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>3143000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-234000</v>
+      </c>
       <c r="W2" t="n">
-        <v>291000</v>
+        <v>9000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6803000</v>
+        <v>-342000</v>
       </c>
       <c r="Z2" t="n">
-        <v>86000</v>
+        <v>3309000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6889000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>-3651000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>26086000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>26086000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>484000</v>
+        <v>-22376000</v>
       </c>
       <c r="AE2" t="n">
-        <v>484000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>-13755000</v>
-      </c>
+        <v>1737000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-24113000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>31856000</v>
+        <v>36462000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3648000</v>
+        <v>-10297000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4530000</v>
+        <v>-23510000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2557000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>4759000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4759000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-6075000</v>
+        <v>-16561000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1668000</v>
+        <v>-12489000</v>
       </c>
       <c r="AO2" t="n">
-        <v>378000</v>
+        <v>1105000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14108000</v>
+        <v>17644000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14108000</v>
+        <v>17644000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2412000</v>
+        <v>-451000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-301000</v>
+        <v>-15000</v>
       </c>
       <c r="AT2" t="n">
-        <v>29454000</v>
+        <v>52471000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>43607000</v>
+        <v>-16807000</v>
       </c>
       <c r="C3" t="n">
-        <v>-32531000</v>
+        <v>-60000000</v>
       </c>
       <c r="D3" t="n">
-        <v>-3000</v>
+        <v>-52463000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>6004000</v>
       </c>
       <c r="F3" t="n">
-        <v>-8679000</v>
+        <v>-17661000</v>
       </c>
       <c r="G3" t="n">
-        <v>37520000</v>
+        <v>21886000</v>
       </c>
       <c r="H3" t="n">
-        <v>21886000</v>
+        <v>58058000</v>
       </c>
       <c r="I3" t="n">
-        <v>-524000</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>16158000</v>
+        <v>-36174000</v>
       </c>
       <c r="K3" t="n">
-        <v>-27980000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13190000</v>
-      </c>
+        <v>-117438000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-2007000</v>
+        <v>-2783000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-32531000</v>
+        <v>-60000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-32531000</v>
+        <v>-60000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3000</v>
+        <v>-46459000</v>
       </c>
       <c r="R3" t="n">
-        <v>-3000</v>
+        <v>-46459000</v>
       </c>
       <c r="S3" t="n">
-        <v>-3000</v>
+        <v>-52463000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6004000</v>
       </c>
       <c r="U3" t="n">
-        <v>-8148000</v>
+        <v>80410000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>434000</v>
+        <v>164000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-757000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>104000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-861000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>95503000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>95503000</v>
       </c>
       <c r="AD3" t="n">
+        <v>2404000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2404000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-17661000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-17661000</v>
+      </c>
+      <c r="AH3" t="n">
         <v>854000</v>
       </c>
-      <c r="AE3" t="n">
-        <v>854000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>-8679000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>52286000</v>
-      </c>
       <c r="AI3" t="n">
-        <v>-796000</v>
+        <v>-15719000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15785000</v>
+        <v>-26854000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-9408000</v>
+        <v>16207000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>7998000</v>
+        <v>-26587000</v>
       </c>
       <c r="AN3" t="n">
-        <v>17817000</v>
+        <v>-16883000</v>
       </c>
       <c r="AO3" t="n">
-        <v>987000</v>
+        <v>2795000</v>
       </c>
       <c r="AP3" t="n">
-        <v>14996000</v>
+        <v>17608000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14996000</v>
+        <v>17608000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-507000</v>
+        <v>-28069000</v>
       </c>
       <c r="AS3" t="n">
-        <v>247000</v>
+        <v>36000</v>
       </c>
       <c r="AT3" t="n">
-        <v>30864000</v>
+        <v>51899000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-16807000</v>
+        <v>43607000</v>
       </c>
       <c r="C4" t="n">
-        <v>-60000000</v>
+        <v>-32531000</v>
       </c>
       <c r="D4" t="n">
-        <v>-52463000</v>
+        <v>-3000</v>
       </c>
       <c r="E4" t="n">
-        <v>6004000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-17661000</v>
+        <v>-8679000</v>
       </c>
       <c r="G4" t="n">
+        <v>37520000</v>
+      </c>
+      <c r="H4" t="n">
         <v>21886000</v>
       </c>
-      <c r="H4" t="n">
-        <v>58058000</v>
-      </c>
       <c r="I4" t="n">
-        <v>2000</v>
+        <v>-524000</v>
       </c>
       <c r="J4" t="n">
-        <v>-36174000</v>
+        <v>16158000</v>
       </c>
       <c r="K4" t="n">
-        <v>-117438000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-27980000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13190000</v>
+      </c>
       <c r="M4" t="n">
-        <v>-2783000</v>
+        <v>-2007000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-60000000</v>
+        <v>-32531000</v>
       </c>
       <c r="P4" t="n">
-        <v>-60000000</v>
+        <v>-32531000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-46459000</v>
+        <v>-3000</v>
       </c>
       <c r="R4" t="n">
-        <v>-46459000</v>
+        <v>-3000</v>
       </c>
       <c r="S4" t="n">
-        <v>-52463000</v>
+        <v>-3000</v>
       </c>
       <c r="T4" t="n">
-        <v>6004000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>80410000</v>
+        <v>-8148000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>164000</v>
+        <v>434000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>-757000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-861000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>95503000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>95503000</v>
-      </c>
       <c r="AD4" t="n">
-        <v>2404000</v>
+        <v>854000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2404000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-17661000</v>
-      </c>
+        <v>854000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-17661000</v>
+        <v>-8679000</v>
       </c>
       <c r="AH4" t="n">
-        <v>854000</v>
+        <v>52286000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-15719000</v>
+        <v>-796000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-26854000</v>
+        <v>15785000</v>
       </c>
       <c r="AK4" t="n">
-        <v>16207000</v>
+        <v>-9408000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-26587000</v>
+        <v>7998000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-16883000</v>
+        <v>17817000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2795000</v>
+        <v>987000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17608000</v>
+        <v>14996000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17608000</v>
+        <v>14996000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-28069000</v>
+        <v>-507000</v>
       </c>
       <c r="AS4" t="n">
-        <v>36000</v>
+        <v>247000</v>
       </c>
       <c r="AT4" t="n">
-        <v>51899000</v>
+        <v>30864000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>12349000</v>
+        <v>18101000</v>
       </c>
       <c r="C5" t="n">
-        <v>-14000</v>
+        <v>-17524000</v>
       </c>
       <c r="D5" t="n">
-        <v>-30039000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>43017000</v>
-      </c>
+        <v>-5000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-24113000</v>
+        <v>-13755000</v>
       </c>
       <c r="G5" t="n">
-        <v>58058000</v>
+        <v>32998000</v>
       </c>
       <c r="H5" t="n">
-        <v>21630000</v>
+        <v>37520000</v>
       </c>
       <c r="I5" t="n">
-        <v>40000</v>
+        <v>270000</v>
       </c>
       <c r="J5" t="n">
-        <v>36388000</v>
+        <v>-4792000</v>
       </c>
       <c r="K5" t="n">
-        <v>-3217000</v>
+        <v>-16865000</v>
       </c>
       <c r="L5" t="n">
-        <v>1826000</v>
+        <v>4408000</v>
       </c>
       <c r="M5" t="n">
-        <v>-908000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-13192000</v>
-      </c>
+        <v>-684000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-14000</v>
+        <v>-17524000</v>
       </c>
       <c r="P5" t="n">
-        <v>-14000</v>
+        <v>-17524000</v>
       </c>
       <c r="Q5" t="n">
-        <v>12978000</v>
+        <v>-5000</v>
       </c>
       <c r="R5" t="n">
-        <v>12978000</v>
+        <v>-5000</v>
       </c>
       <c r="S5" t="n">
-        <v>-30039000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>43017000</v>
-      </c>
+        <v>-5000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>3143000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-234000</v>
-      </c>
+        <v>-19783000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>9000</v>
+        <v>291000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-342000</v>
+        <v>-6803000</v>
       </c>
       <c r="Z5" t="n">
-        <v>3309000</v>
+        <v>86000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3651000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>26086000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>26086000</v>
-      </c>
+        <v>-6889000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-22376000</v>
+        <v>484000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-24113000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>484000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>-13755000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>36462000</v>
+        <v>31856000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10297000</v>
+        <v>-3648000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-23510000</v>
+        <v>-4530000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4759000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>4759000</v>
-      </c>
+        <v>2557000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-16561000</v>
+        <v>-6075000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-12489000</v>
+        <v>-1668000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1105000</v>
+        <v>378000</v>
       </c>
       <c r="AP5" t="n">
-        <v>17644000</v>
+        <v>14108000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17644000</v>
+        <v>14108000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-451000</v>
+        <v>-2412000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-15000</v>
+        <v>-301000</v>
       </c>
       <c r="AT5" t="n">
-        <v>52471000</v>
+        <v>29454000</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU2"/>
+  <dimension ref="A1:DW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,470 +3522,480 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>debtToEquity</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4059,7 +4069,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Lentex S.A. manufactures and sells flexible PVC floor coverings for residential and commercial areas, and sports facilities in Poland and internationally. The company offers nonwovens fabrics, including nonwoven interlinings, waddings, and spunlace fabrics. Its products are used for sanitary, technical, automotive, construction, furniture, clothing, shoe making, agricultural, filtration, and other applications. The company was founded in 1911 and is headquartered in Lubliniec, Poland.</t>
+          <t>Lentex S.A. manufactures and sells flexible PVC floor coverings for residential and commercial areas, and sports facilities in Poland and internationally. The company offers nonwovens fabrics, including nonwoven interlinings, waddings, and spunlace fabrics. Its products are used for automotive, sanitary, furniture, clothing, needle-punched nonwovens and bentonite mats, filtration, silicone down, and protective mats. The company was founded in 1911 and is headquartered in Lubliniec, Poland.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4082,34 +4092,34 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="X2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.51</v>
+        <v>1.525</v>
       </c>
       <c r="AB2" t="n">
         <v>0.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.57</v>
+        <v>9.83</v>
       </c>
       <c r="AD2" t="n">
         <v>1782777600</v>
@@ -4118,16 +4128,16 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.099999</v>
+        <v>0.038</v>
       </c>
       <c r="AG2" t="n">
-        <v>575</v>
+        <v>15.25</v>
       </c>
       <c r="AH2" t="n">
         <v>575</v>
       </c>
       <c r="AI2" t="n">
-        <v>9</v>
+        <v>575</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -4136,311 +4146,317 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.475</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.805</v>
+        <v>1.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>51313924</v>
+        <v>1.815</v>
       </c>
       <c r="AO2" t="n">
-        <v>56466987</v>
+        <v>51823664</v>
       </c>
       <c r="AP2" t="n">
+        <v>58044330</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>1.295</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.705</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>2.35</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>1.295</v>
       </c>
-      <c r="AT2" t="n">
-        <v>1.5593</v>
-      </c>
       <c r="AU2" t="n">
-        <v>1.523425</v>
+        <v>1.5521</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.5136</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="AY2" t="b">
+      <c r="AZ2" t="b">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>0.062750004</v>
       </c>
-      <c r="BA2" t="n">
-        <v>1983054</v>
-      </c>
       <c r="BB2" t="n">
+        <v>2064791</v>
+      </c>
+      <c r="BC2" t="n">
         <v>33982733</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>0.67947996</v>
       </c>
-      <c r="BD2" t="n">
-        <v>0.00055</v>
-      </c>
       <c r="BE2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BF2" t="n">
         <v>33982733</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>7.391</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0.20430253</v>
-      </c>
       <c r="BH2" t="n">
+        <v>0.20633203</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>-0.199</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>0.1</v>
       </c>
-      <c r="BM2" t="n">
-        <v>-0.0129032135</v>
-      </c>
       <c r="BN2" t="n">
-        <v>0.27294624</v>
+        <v>0.0033669472</v>
       </c>
       <c r="BO2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BP2" t="n">
         <v>0.62</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>1782777600</v>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BR2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BS2" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="BT2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BT2" t="n">
-        <v>36372000</v>
-      </c>
       <c r="BU2" t="n">
-        <v>2.441</v>
+        <v>36168000</v>
       </c>
       <c r="BV2" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="BW2" t="n">
         <v>4.236</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.0298</v>
-      </c>
       <c r="BX2" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>0.04435</v>
       </c>
-      <c r="BY2" t="n">
-        <v>7336875</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-0.111</v>
-      </c>
       <c r="CA2" t="n">
+        <v>5345625</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-0.146</v>
+      </c>
+      <c r="CC2" t="n">
         <v>-0.076</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CD2" t="n">
         <v>0.21068001</v>
       </c>
-      <c r="CC2" t="n">
-        <v>0.12028</v>
-      </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
+        <v>0.119610004</v>
+      </c>
+      <c r="CF2" t="n">
         <v>0</v>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>0KM.F</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CK2" t="b">
+      <c r="CM2" t="b">
         <v>0</v>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>LENTEX S.A.                   I</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CP2" t="n">
+        <v>2.3489912</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>finmb_734805</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CV2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="CX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>[{'header': 'Dividend', 'message': '0KM.F announced a cash dividend of EUR 0.62 with an ex-date of Jun. 30, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1782770400000, 'amount': '0.62'}}]</t>
         </is>
       </c>
-      <c r="CO2" t="n">
-        <v>1780380267</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>-1.3071884</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CR2" t="inlineStr">
+      <c r="DA2" t="n">
+        <v>1782108751</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.027099967</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.017460195</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.011399984</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.007531702</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1617256800000</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.034999967</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1.525 - 1.525</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.23000002</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.1776062</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1.295 - 1.705</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.18000007</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.10557188</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.33669472</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>Lentex S.A.</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>finmb_734805</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1617256800000</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.01999998</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>1.51 - 1.51</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>9</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.21500003</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.1660232</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>1.295 - 1.705</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.19500005</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.11436953</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-1.2903214</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.049299955</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.031616725</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.013424993</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.008812375000000001</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
